--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_GD.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_GD.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rbc5417562ee14e90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Raf0c142820764187"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rf5e997ca977d4c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Re34e58e0b1dc4bd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rc9a97b639d7e4595"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R764eac7edf3541e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Re0cc74d8a4f24759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rd3b7335789774b95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R608e91537fed42c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rb4fa63b942684d2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R325171ee1b06486b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R55e239cbaeb44702"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R1faed109532e4ef2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Ra1f82e510ad54d98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R2ef44826d3e14ceb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R2ac91e856ad947be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Rf4b57a097a8b41dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R6e2ffcacf9404b8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R5ff9daa8a5f64e8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rc4819107ad524224"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rbbdf99781bc048d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R9cf334b2f34a4294"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rd20092470dd241b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R29deed97e12b45bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R4c87f3a4811b491a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Ra348bee117e74027"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R41a67ae563964a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R42f281386c8f4e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rc83d5a9749474569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R3865c4eb9d864c02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R55c8d4355c874027"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R6233d3d2e09643b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R6911f0491ce649e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R4cf2061c35b24b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R5ff84e7a2c2e491d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R975f069cab2348fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rc11b8a91fd3a41b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Rafe9c304f9874578"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rbc909dd59ab8458e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rae617ee780b843ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R2633791274044e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R2571788c35d3489c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R5430bcd467814c69"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4204,6 +4205,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>イングリッド</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>冬の山</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14.25"/>
